--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_48.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_48.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5962828.089285962</v>
+        <v>5922801.996532566</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645789</v>
+        <v>6767152.318645786</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645789</v>
+        <v>6767152.318645786</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517487</v>
+        <v>2916902.906517474</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517487</v>
+        <v>2916902.906517474</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36439165.04109511</v>
+        <v>36439165.04109512</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>174.6089458300098</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -678,25 +678,25 @@
         <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
-        <v>418.7382696589336</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>97.12488247690067</v>
+        <v>97.1248824769005</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>297.9910820919849</v>
       </c>
       <c r="N2" t="n">
-        <v>814</v>
+        <v>194.5855355810472</v>
       </c>
       <c r="O2" t="n">
-        <v>814</v>
+        <v>650.9664887921559</v>
       </c>
       <c r="P2" t="n">
-        <v>410.6151547142695</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>370.9706110579117</v>
@@ -705,10 +705,10 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T2" t="n">
-        <v>186.6755817285639</v>
+        <v>279.285214602999</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -723,7 +723,7 @@
         <v>592.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>284.6463592929431</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>147.4295318620688</v>
       </c>
       <c r="R3" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
@@ -845,10 +845,10 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>91.42153354832159</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
-        <v>171.1850752716849</v>
+        <v>141.9749974174622</v>
       </c>
       <c r="O4" t="n">
         <v>240.445564079015</v>
@@ -930,13 +930,13 @@
         <v>194.5855355810472</v>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>814</v>
       </c>
-      <c r="P5" t="n">
-        <v>216.0296191332216</v>
-      </c>
       <c r="Q5" t="n">
-        <v>370.9706110579117</v>
+        <v>587.0002301911337</v>
       </c>
       <c r="R5" t="n">
         <v>250.8785988282945</v>
@@ -945,22 +945,22 @@
         <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
       </c>
       <c r="V5" t="n">
-        <v>322.4606570412591</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>111.3174326828064</v>
+        <v>203.9270655572416</v>
       </c>
     </row>
     <row r="6">
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1015,16 +1015,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>96.62571193790353</v>
       </c>
       <c r="R6" t="n">
-        <v>147.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>63.08338960093648</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
@@ -1033,10 +1033,10 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>297.392050126921</v>
+        <v>320.9396782847023</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,34 +1143,34 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>97.32676367243049</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
         <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>97.12488247690055</v>
+        <v>814</v>
       </c>
       <c r="L8" t="n">
-        <v>650.9664887921559</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>297.9910820919849</v>
       </c>
       <c r="N8" t="n">
-        <v>194.5855355810472</v>
+        <v>194.5855355810518</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P8" t="n">
-        <v>814</v>
+        <v>313.1545016101224</v>
       </c>
       <c r="Q8" t="n">
         <v>370.9706110579117</v>
@@ -1185,10 +1185,10 @@
         <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
-        <v>649.2212965486107</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
-        <v>229.8510241668239</v>
+        <v>573.3392558695535</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>57.72562438342279</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1252,13 +1252,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>431.9201565853224</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>466.5639999646113</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
         <v>5.357765217513816</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617060972</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>297.392050126921</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>133.3338276497441</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
         <v>185.3391557398498</v>
@@ -1377,10 +1377,10 @@
         <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>183.0096587035274</v>
@@ -1422,10 +1422,10 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>424.2212965486107</v>
+        <v>0.5590901007588536</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>413.3734759809475</v>
@@ -1434,7 +1434,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>199.1027092550209</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>86.85759952868681</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y13" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1605,10 +1605,10 @@
         <v>230.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>198.4745782429939</v>
+        <v>118.1404976552745</v>
       </c>
       <c r="D14" t="n">
-        <v>159.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>153.3632896068686</v>
@@ -1656,7 +1656,7 @@
         <v>243.8481678023229</v>
       </c>
       <c r="T14" t="n">
-        <v>96.00234540099424</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U14" t="n">
         <v>398.2212965486107</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>29.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>23.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3775199254117115</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>53.74128073011011</v>
       </c>
       <c r="Q16" t="n">
         <v>474.839266425598</v>
@@ -1848,10 +1848,10 @@
         <v>131.3391557398498</v>
       </c>
       <c r="E17" t="n">
-        <v>124.9326809922826</v>
+        <v>125.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>125.8896287080119</v>
+        <v>125.4590200934258</v>
       </c>
       <c r="G17" t="n">
         <v>124.7573722870162</v>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>415.2745579018177</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>125.4590200934258</v>
+        <v>125.8896287080119</v>
       </c>
       <c r="G20" t="n">
         <v>124.7573722870162</v>
       </c>
       <c r="H20" t="n">
-        <v>129.0096587035274</v>
+        <v>128.5790500889954</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2273,19 +2273,19 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>286.3057184137641</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>338.6387678008247</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>377.7929984536983</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>179.3632896068686</v>
@@ -2565,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2604,10 +2604,10 @@
         <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>203.1218718293226</v>
       </c>
       <c r="U26" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>404.8510241668239</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>117.6084466343095</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2711,22 +2711,22 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>60.53621805555548</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>58.5191620052898</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>80.97384045563096</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y28" t="n">
         <v>62.46535284946236</v>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
         <v>224.4745782429939</v>
@@ -2838,7 +2838,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
-        <v>9.646769863628542</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>361.6755817285639</v>
@@ -2853,10 +2853,10 @@
         <v>413.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>367.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>286.3174326828064</v>
+        <v>136.3985552492047</v>
       </c>
     </row>
     <row r="30">
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>281.6133912716818</v>
       </c>
       <c r="O31" t="n">
-        <v>345.920735428856</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -3045,34 +3045,34 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>377.7382696589747</v>
       </c>
       <c r="K32" t="n">
-        <v>773</v>
+        <v>10.23281455315225</v>
       </c>
       <c r="L32" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>654.6988358539121</v>
+        <v>324.5128000159259</v>
       </c>
       <c r="N32" t="n">
-        <v>107.6934676571269</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>329.9706110579529</v>
+        <v>757.61730000004</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S32" t="n">
         <v>203.8481678023229</v>
@@ -3212,25 +3212,25 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>109.2047614405202</v>
+        <v>142.7105576529391</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3285,28 +3285,28 @@
         <v>8.45659138541424</v>
       </c>
       <c r="J35" t="n">
-        <v>757.6173000000474</v>
+        <v>377.738269658982</v>
       </c>
       <c r="K35" t="n">
-        <v>712.6384842278635</v>
+        <v>10.23281455316345</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M35" t="n">
         <v>256.9910820920331</v>
       </c>
       <c r="N35" t="n">
-        <v>531.2370179081564</v>
+        <v>153.5855355810957</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="Q35" t="n">
-        <v>757.6173000000472</v>
+        <v>671.5534823429068</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3449,28 +3449,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P37" t="n">
-        <v>301.7315509081865</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>434.839266425598</v>
+        <v>310.8612858437193</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>190.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>166.9311696284081</v>
+        <v>158.4745782429939</v>
       </c>
       <c r="D38" t="n">
         <v>119.3391557398498</v>
@@ -3525,19 +3525,19 @@
         <v>377.7382696589893</v>
       </c>
       <c r="K38" t="n">
-        <v>351.8156858381913</v>
+        <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>727.107932076245</v>
       </c>
       <c r="M38" t="n">
         <v>256.9910820920404</v>
       </c>
       <c r="N38" t="n">
-        <v>153.5855355811029</v>
+        <v>551.2932893430122</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000557</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>329.9706110579674</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S38" t="n">
         <v>203.8481678023229</v>
@@ -3686,19 +3686,19 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>154.0941037942843</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>23.65946653203068</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>434.839266425598</v>
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3738,19 +3738,19 @@
         <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>236.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>190.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>195.0096587035274</v>
@@ -3786,19 +3786,19 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>281.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>373.6755817285639</v>
       </c>
       <c r="U41" t="n">
-        <v>358.643437969703</v>
+        <v>259.0971620062078</v>
       </c>
       <c r="V41" t="n">
         <v>416.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>425.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>379.2818334606677</v>
@@ -3835,7 +3835,7 @@
         <v>119.1680871864211</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>4.126385891348534</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3865,22 +3865,22 @@
         <v>334.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>166.5605010734961</v>
+        <v>253.5639999646113</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>192.3577652175138</v>
       </c>
       <c r="U42" t="n">
         <v>187.2103597601867</v>
       </c>
       <c r="V42" t="n">
-        <v>201.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>219.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>206.8627394453875</v>
+        <v>124.8857566369305</v>
       </c>
       <c r="Y42" t="n">
         <v>186.3913927661343</v>
@@ -3905,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>61.38285596774193</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>225.731879461114</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>287.1147354288559</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3981,13 +3981,13 @@
         <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>217.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>217.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>216.7573722870162</v>
       </c>
       <c r="H44" t="n">
         <v>221.0096587035274</v>
@@ -4020,19 +4020,19 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
         <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>17.02240302848644</v>
+        <v>399.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>462.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>16.29543634009137</v>
       </c>
       <c r="W44" t="n">
         <v>451.3734759809475</v>
@@ -4057,10 +4057,10 @@
         <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>160.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>155.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>152.6362423378769</v>
@@ -4102,19 +4102,19 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>279.5639999646113</v>
+        <v>95.99613065420759</v>
       </c>
       <c r="T45" t="n">
         <v>218.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>213.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>87.1222556952586</v>
+        <v>245.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>232.8627394453875</v>
@@ -4142,13 +4142,13 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>87.38285596774193</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41.77112610161862</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4169,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.644875690224744</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>144.6631741191209</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>23.02456650625771</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4321,22 +4321,22 @@
         <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>448.0120508495621</v>
+        <v>65.12</v>
       </c>
       <c r="K2" t="n">
-        <v>1155.766108953703</v>
+        <v>772.8740581041409</v>
       </c>
       <c r="L2" t="n">
-        <v>1961.626108953703</v>
+        <v>756.5118358819186</v>
       </c>
       <c r="M2" t="n">
-        <v>2466.485015931496</v>
+        <v>1261.370742859712</v>
       </c>
       <c r="N2" t="n">
-        <v>2450.122793709274</v>
+        <v>1870.67969681825</v>
       </c>
       <c r="O2" t="n">
-        <v>2433.760571487051</v>
+        <v>2018.997788947385</v>
       </c>
       <c r="P2" t="n">
         <v>2824.857788947385</v>
@@ -4348,25 +4348,25 @@
         <v>3002.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>2906.781043807457</v>
+        <v>2502.740639767053</v>
       </c>
       <c r="T2" t="n">
-        <v>2718.219850142241</v>
+        <v>2220.634362390286</v>
       </c>
       <c r="U2" t="n">
-        <v>2466.481166759806</v>
+        <v>1968.895679007851</v>
       </c>
       <c r="V2" t="n">
-        <v>2234.308415076146</v>
+        <v>1736.722927324191</v>
       </c>
       <c r="W2" t="n">
-        <v>1589.486722166097</v>
+        <v>1091.901234414143</v>
       </c>
       <c r="X2" t="n">
-        <v>991.2222439229987</v>
+        <v>493.6367561710438</v>
       </c>
       <c r="Y2" t="n">
-        <v>474.7399886878407</v>
+        <v>381.1949049762899</v>
       </c>
     </row>
     <row r="3">
@@ -4376,19 +4376,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>352.6415750433769</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="C3" t="n">
-        <v>352.6415750433769</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="D3" t="n">
-        <v>352.6415750433769</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="E3" t="n">
-        <v>352.6415750433769</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="F3" t="n">
-        <v>352.6415750433769</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="G3" t="n">
         <v>65.12</v>
@@ -4421,31 +4421,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1045.724879873102</v>
+        <v>1071.633701315941</v>
       </c>
       <c r="R3" t="n">
-        <v>492.9230644262537</v>
+        <v>922.8722899094971</v>
       </c>
       <c r="S3" t="n">
-        <v>425.6867008256363</v>
+        <v>855.6359263088797</v>
       </c>
       <c r="T3" t="n">
-        <v>420.2748167675415</v>
+        <v>850.2240422507849</v>
       </c>
       <c r="U3" t="n">
-        <v>420.0623321612923</v>
+        <v>850.0115576445356</v>
       </c>
       <c r="V3" t="n">
-        <v>405.4050925738982</v>
+        <v>835.3543180571415</v>
       </c>
       <c r="W3" t="n">
-        <v>372.704948220536</v>
+        <v>802.6541737037794</v>
       </c>
       <c r="X3" t="n">
-        <v>352.6415750433769</v>
+        <v>782.5908005266202</v>
       </c>
       <c r="Y3" t="n">
-        <v>352.6415750433769</v>
+        <v>782.5908005266202</v>
       </c>
     </row>
     <row r="4">
@@ -4455,40 +4455,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>624.11335726399</v>
+        <v>741.9879361380767</v>
       </c>
       <c r="C4" t="n">
-        <v>750.1153630824258</v>
+        <v>867.9899419565126</v>
       </c>
       <c r="D4" t="n">
-        <v>863.4345072074259</v>
+        <v>981.3090860815126</v>
       </c>
       <c r="E4" t="n">
-        <v>981.2634114188389</v>
+        <v>1099.137990292926</v>
       </c>
       <c r="F4" t="n">
-        <v>1105.624384010775</v>
+        <v>1223.498962884861</v>
       </c>
       <c r="G4" t="n">
-        <v>1214.924801058187</v>
+        <v>1376.905528771747</v>
       </c>
       <c r="H4" t="n">
-        <v>1214.924801058187</v>
+        <v>1546.422113931144</v>
       </c>
       <c r="I4" t="n">
-        <v>1436.05767999427</v>
+        <v>1546.422113931144</v>
       </c>
       <c r="J4" t="n">
-        <v>1436.05767999427</v>
+        <v>1546.422113931144</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931139</v>
+        <v>1546.422113931144</v>
       </c>
       <c r="L4" t="n">
-        <v>1522.636630943483</v>
+        <v>1522.636630943488</v>
       </c>
       <c r="M4" t="n">
-        <v>1430.29164756134</v>
+        <v>1400.78651841566</v>
       </c>
       <c r="N4" t="n">
         <v>1257.377430115193</v>
@@ -4506,25 +4506,25 @@
         <v>65.12</v>
       </c>
       <c r="S4" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T4" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="U4" t="n">
-        <v>102.3702550941731</v>
+        <v>195.8995885088814</v>
       </c>
       <c r="V4" t="n">
-        <v>301.1916479801191</v>
+        <v>195.8995885088814</v>
       </c>
       <c r="W4" t="n">
-        <v>473.0825662397965</v>
+        <v>367.7905067685588</v>
       </c>
       <c r="X4" t="n">
-        <v>624.11335726399</v>
+        <v>518.8212977927523</v>
       </c>
       <c r="Y4" t="n">
-        <v>624.11335726399</v>
+        <v>630.2305984717846</v>
       </c>
     </row>
     <row r="5">
@@ -4573,10 +4573,10 @@
         <v>2253.571747667811</v>
       </c>
       <c r="O5" t="n">
-        <v>2237.209525445589</v>
+        <v>3059.431747667812</v>
       </c>
       <c r="P5" t="n">
-        <v>2824.857788947385</v>
+        <v>3043.06952544559</v>
       </c>
       <c r="Q5" t="n">
         <v>3256</v>
@@ -4588,19 +4588,19 @@
         <v>2502.740639767053</v>
       </c>
       <c r="T5" t="n">
-        <v>2314.179446101837</v>
+        <v>1910.139042061433</v>
       </c>
       <c r="U5" t="n">
-        <v>2062.440762719402</v>
+        <v>1658.400358678998</v>
       </c>
       <c r="V5" t="n">
-        <v>1736.722927324191</v>
+        <v>1426.227606995337</v>
       </c>
       <c r="W5" t="n">
-        <v>1495.941638454547</v>
+        <v>1185.446318125693</v>
       </c>
       <c r="X5" t="n">
-        <v>897.6771602114478</v>
+        <v>991.2222439229986</v>
       </c>
       <c r="Y5" t="n">
         <v>785.2353090166939</v>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="C6" t="n">
         <v>65.12</v>
@@ -4658,31 +4658,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1220.552420368536</v>
+        <v>1122.95069113833</v>
       </c>
       <c r="R6" t="n">
-        <v>1071.791008962092</v>
+        <v>570.1488756914822</v>
       </c>
       <c r="S6" t="n">
-        <v>1004.554645361474</v>
+        <v>502.9125120908647</v>
       </c>
       <c r="T6" t="n">
-        <v>940.8340498049729</v>
+        <v>497.50062803277</v>
       </c>
       <c r="U6" t="n">
-        <v>940.6215651987236</v>
+        <v>497.2881434265207</v>
       </c>
       <c r="V6" t="n">
-        <v>925.9643256113295</v>
+        <v>482.6309038391266</v>
       </c>
       <c r="W6" t="n">
-        <v>489.2237772175632</v>
+        <v>449.9307594857645</v>
       </c>
       <c r="X6" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="Y6" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>654.3215332949673</v>
+        <v>524.3582863254435</v>
       </c>
       <c r="C7" t="n">
-        <v>654.3215332949673</v>
+        <v>650.3602921438793</v>
       </c>
       <c r="D7" t="n">
-        <v>767.6406774199673</v>
+        <v>650.3602921438793</v>
       </c>
       <c r="E7" t="n">
-        <v>767.6406774199673</v>
+        <v>767.6406774199693</v>
       </c>
       <c r="F7" t="n">
-        <v>892.0016500119028</v>
+        <v>892.0016500119048</v>
       </c>
       <c r="G7" t="n">
-        <v>1045.408215898788</v>
+        <v>1045.40821589879</v>
       </c>
       <c r="H7" t="n">
-        <v>1214.924801058186</v>
+        <v>1214.924801058188</v>
       </c>
       <c r="I7" t="n">
-        <v>1436.057679994269</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="J7" t="n">
-        <v>1436.057679994269</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931137</v>
+        <v>1546.422113931139</v>
       </c>
       <c r="L7" t="n">
-        <v>1522.636630943481</v>
+        <v>1546.422113931139</v>
       </c>
       <c r="M7" t="n">
-        <v>1400.786518415653</v>
+        <v>1424.572001403311</v>
       </c>
       <c r="N7" t="n">
-        <v>1227.872300969507</v>
+        <v>1251.657783957164</v>
       </c>
       <c r="O7" t="n">
-        <v>984.9979938189864</v>
+        <v>1008.783476806644</v>
       </c>
       <c r="P7" t="n">
-        <v>694.6465823762819</v>
+        <v>718.4320653639397</v>
       </c>
       <c r="Q7" t="n">
-        <v>365.5160102292132</v>
+        <v>389.301493216871</v>
       </c>
       <c r="R7" t="n">
         <v>65.12</v>
@@ -4746,22 +4746,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>172.1999214703116</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="U7" t="n">
-        <v>172.1999214703116</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="V7" t="n">
-        <v>371.0213143562576</v>
+        <v>301.1916479801191</v>
       </c>
       <c r="W7" t="n">
-        <v>542.912232615935</v>
+        <v>301.1916479801191</v>
       </c>
       <c r="X7" t="n">
-        <v>542.912232615935</v>
+        <v>301.1916479801191</v>
       </c>
       <c r="Y7" t="n">
-        <v>654.3215332949673</v>
+        <v>412.6009486591514</v>
       </c>
     </row>
     <row r="8">
@@ -4771,46 +4771,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1049.365529973416</v>
+        <v>1106.448124213083</v>
       </c>
       <c r="C8" t="n">
-        <v>999.3912085158468</v>
+        <v>1056.473802755514</v>
       </c>
       <c r="D8" t="n">
-        <v>584.9072128190287</v>
+        <v>641.9898070586958</v>
       </c>
       <c r="E8" t="n">
-        <v>580.4998495797674</v>
+        <v>637.5824438194345</v>
       </c>
       <c r="F8" t="n">
-        <v>575.5608306827858</v>
+        <v>632.6434249224528</v>
       </c>
       <c r="G8" t="n">
-        <v>477.2509683874014</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H8" t="n">
-        <v>65.12</v>
+        <v>216.7171309926107</v>
       </c>
       <c r="I8" t="n">
         <v>65.12</v>
       </c>
       <c r="J8" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>772.8740581041409</v>
+        <v>431.6498286273397</v>
       </c>
       <c r="L8" t="n">
-        <v>921.1921502332762</v>
+        <v>1237.50982862734</v>
       </c>
       <c r="M8" t="n">
-        <v>1426.051057211069</v>
+        <v>1742.368735605133</v>
       </c>
       <c r="N8" t="n">
-        <v>2035.360011169607</v>
+        <v>2351.677689563671</v>
       </c>
       <c r="O8" t="n">
-        <v>2841.220011169607</v>
+        <v>2335.315467341448</v>
       </c>
       <c r="P8" t="n">
         <v>2824.857788947385</v>
@@ -4828,19 +4828,19 @@
         <v>2567.592172191023</v>
       </c>
       <c r="U8" t="n">
-        <v>1911.813084768184</v>
+        <v>2315.853488808588</v>
       </c>
       <c r="V8" t="n">
-        <v>1679.640333084524</v>
+        <v>1736.722927324191</v>
       </c>
       <c r="W8" t="n">
-        <v>1438.85904421488</v>
+        <v>1495.941638454547</v>
       </c>
       <c r="X8" t="n">
-        <v>1244.634970012185</v>
+        <v>1301.717564251852</v>
       </c>
       <c r="Y8" t="n">
-        <v>1132.193118817431</v>
+        <v>1189.275713057098</v>
       </c>
     </row>
     <row r="9">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65.12</v>
+        <v>123.4287114984069</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12</v>
+        <v>123.4287114984069</v>
       </c>
       <c r="D9" t="n">
-        <v>65.12</v>
+        <v>123.4287114984069</v>
       </c>
       <c r="E9" t="n">
-        <v>65.12</v>
+        <v>123.4287114984069</v>
       </c>
       <c r="F9" t="n">
         <v>65.12</v>
@@ -4895,31 +4895,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1045.724879873102</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>609.4418934232809</v>
+        <v>667.7506049216878</v>
       </c>
       <c r="S9" t="n">
-        <v>138.1651257822594</v>
+        <v>600.5142413210704</v>
       </c>
       <c r="T9" t="n">
-        <v>132.7532417241646</v>
+        <v>595.1023572629756</v>
       </c>
       <c r="U9" t="n">
-        <v>132.5407571179154</v>
+        <v>594.8898726567263</v>
       </c>
       <c r="V9" t="n">
-        <v>117.8835175305213</v>
+        <v>580.2326330693322</v>
       </c>
       <c r="W9" t="n">
-        <v>85.18337317715914</v>
+        <v>547.5324887159701</v>
       </c>
       <c r="X9" t="n">
-        <v>65.12</v>
+        <v>123.4287114984069</v>
       </c>
       <c r="Y9" t="n">
-        <v>65.12</v>
+        <v>123.4287114984069</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>697.8361126359287</v>
+        <v>550.420780645014</v>
       </c>
       <c r="C10" t="n">
-        <v>823.8381184543645</v>
+        <v>676.4227864634498</v>
       </c>
       <c r="D10" t="n">
-        <v>937.1572625793646</v>
+        <v>789.7419305884499</v>
       </c>
       <c r="E10" t="n">
-        <v>937.1572625793646</v>
+        <v>907.570834799863</v>
       </c>
       <c r="F10" t="n">
-        <v>1061.5182351713</v>
+        <v>1031.931807391798</v>
       </c>
       <c r="G10" t="n">
-        <v>1214.924801058185</v>
+        <v>1185.338373278684</v>
       </c>
       <c r="H10" t="n">
-        <v>1214.924801058185</v>
+        <v>1185.338373278684</v>
       </c>
       <c r="I10" t="n">
-        <v>1436.057679994268</v>
+        <v>1185.338373278684</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994268</v>
+        <v>1546.422113931135</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931137</v>
+        <v>1546.422113931135</v>
       </c>
       <c r="L10" t="n">
-        <v>1522.636630943481</v>
+        <v>1546.422113931135</v>
       </c>
       <c r="M10" t="n">
-        <v>1400.786518415653</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1227.872300969507</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O10" t="n">
-        <v>984.9979938189864</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P10" t="n">
-        <v>694.6465823762819</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>365.5160102292132</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R10" t="n">
         <v>65.12</v>
@@ -4983,22 +4983,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T10" t="n">
-        <v>102.3702550941731</v>
+        <v>115.741733694851</v>
       </c>
       <c r="U10" t="n">
-        <v>302.7785560309268</v>
+        <v>115.741733694851</v>
       </c>
       <c r="V10" t="n">
-        <v>302.7785560309268</v>
+        <v>115.741733694851</v>
       </c>
       <c r="W10" t="n">
-        <v>474.6694742906043</v>
+        <v>287.6326519545284</v>
       </c>
       <c r="X10" t="n">
-        <v>474.6694742906043</v>
+        <v>438.6634429787219</v>
       </c>
       <c r="Y10" t="n">
-        <v>586.0787749696366</v>
+        <v>438.6634429787219</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1115.314881510119</v>
+        <v>845.1065477709494</v>
       </c>
       <c r="C11" t="n">
-        <v>980.6342475204788</v>
+        <v>618.364549545703</v>
       </c>
       <c r="D11" t="n">
-        <v>793.4229790963881</v>
+        <v>431.1532811216122</v>
       </c>
       <c r="E11" t="n">
-        <v>612.24793908945</v>
+        <v>249.9782411146742</v>
       </c>
       <c r="F11" t="n">
-        <v>430.5412434247916</v>
+        <v>249.9782411146742</v>
       </c>
       <c r="G11" t="n">
         <v>249.9782411146742</v>
@@ -5032,25 +5032,25 @@
         <v>65.12</v>
       </c>
       <c r="J11" t="n">
-        <v>65.12</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>520.2108514963016</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1326.070851496302</v>
+        <v>1693.331756443634</v>
       </c>
       <c r="M11" t="n">
-        <v>1836.919680225237</v>
+        <v>2204.180585172569</v>
       </c>
       <c r="N11" t="n">
-        <v>2450.14</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>2450.14</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>3256</v>
@@ -5065,19 +5065,19 @@
         <v>2591.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2163.450863729503</v>
+        <v>2591.392486404101</v>
       </c>
       <c r="V11" t="n">
-        <v>2163.450863729503</v>
+        <v>2182.452057952764</v>
       </c>
       <c r="W11" t="n">
-        <v>1745.901898092182</v>
+        <v>1764.903092315443</v>
       </c>
       <c r="X11" t="n">
-        <v>1374.910147121811</v>
+        <v>1393.911341345072</v>
       </c>
       <c r="Y11" t="n">
-        <v>1374.910147121811</v>
+        <v>1104.701813382641</v>
       </c>
     </row>
     <row r="12">
@@ -5108,28 +5108,28 @@
         <v>65.12</v>
       </c>
       <c r="I12" t="n">
-        <v>72.91487796756496</v>
+        <v>65.12</v>
       </c>
       <c r="J12" t="n">
-        <v>419.6213981428639</v>
+        <v>411.826520175299</v>
       </c>
       <c r="K12" t="n">
-        <v>831.5642142372474</v>
+        <v>823.7693362696824</v>
       </c>
       <c r="L12" t="n">
-        <v>1173.241905939123</v>
+        <v>1317.869797864882</v>
       </c>
       <c r="M12" t="n">
-        <v>1482.072447681982</v>
+        <v>1626.700339607742</v>
       </c>
       <c r="N12" t="n">
-        <v>1838.102732289551</v>
+        <v>1786.701204729125</v>
       </c>
       <c r="O12" t="n">
-        <v>2299.895183973269</v>
+        <v>2248.493656412844</v>
       </c>
       <c r="P12" t="n">
-        <v>2635.174528442776</v>
+        <v>2583.773000882351</v>
       </c>
       <c r="Q12" t="n">
         <v>2635.174528442776</v>
@@ -5166,19 +5166,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>126.2676950056116</v>
+        <v>240.0016972669426</v>
       </c>
       <c r="C13" t="n">
-        <v>126.2676950056116</v>
+        <v>191.7943774204329</v>
       </c>
       <c r="D13" t="n">
-        <v>65.12</v>
+        <v>191.7943774204329</v>
       </c>
       <c r="E13" t="n">
-        <v>65.12</v>
+        <v>135.2480088982545</v>
       </c>
       <c r="F13" t="n">
-        <v>65.12</v>
+        <v>85.36633620356569</v>
       </c>
       <c r="G13" t="n">
         <v>65.12</v>
@@ -5208,34 +5208,34 @@
         <v>300.8366195885342</v>
       </c>
       <c r="P13" t="n">
-        <v>99.72277185618992</v>
+        <v>300.8366195885342</v>
       </c>
       <c r="Q13" t="n">
-        <v>99.72277185618992</v>
+        <v>213.1016705696587</v>
       </c>
       <c r="R13" t="n">
-        <v>99.72277185618992</v>
+        <v>213.1016705696587</v>
       </c>
       <c r="S13" t="n">
-        <v>99.72277185618992</v>
+        <v>213.1016705696587</v>
       </c>
       <c r="T13" t="n">
-        <v>114.5484510149948</v>
+        <v>227.9273497284635</v>
       </c>
       <c r="U13" t="n">
-        <v>187.8496436532814</v>
+        <v>301.2285423667502</v>
       </c>
       <c r="V13" t="n">
-        <v>213.4210365392274</v>
+        <v>326.7999352526961</v>
       </c>
       <c r="W13" t="n">
-        <v>212.0343599344701</v>
+        <v>325.4132586479388</v>
       </c>
       <c r="X13" t="n">
-        <v>189.3640110151696</v>
+        <v>302.7429097286383</v>
       </c>
       <c r="Y13" t="n">
-        <v>126.2676950056116</v>
+        <v>302.7429097286383</v>
       </c>
     </row>
     <row r="14">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>895.5001121224765</v>
+        <v>653.4059340138207</v>
       </c>
       <c r="C14" t="n">
-        <v>695.0207401598564</v>
+        <v>534.0720979983919</v>
       </c>
       <c r="D14" t="n">
         <v>534.0720979983919</v>
@@ -5269,25 +5269,25 @@
         <v>65.12</v>
       </c>
       <c r="J14" t="n">
-        <v>456.4291130376557</v>
+        <v>65.12</v>
       </c>
       <c r="K14" t="n">
-        <v>1166.135479385524</v>
+        <v>774.8263663478684</v>
       </c>
       <c r="L14" t="n">
-        <v>1971.995479385524</v>
+        <v>1580.686366347868</v>
       </c>
       <c r="M14" t="n">
-        <v>2482.844308114459</v>
+        <v>1580.686366347869</v>
       </c>
       <c r="N14" t="n">
-        <v>3096.064627889222</v>
+        <v>1580.686366347869</v>
       </c>
       <c r="O14" t="n">
-        <v>3256</v>
+        <v>2386.546366347869</v>
       </c>
       <c r="P14" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>3256</v>
@@ -5299,22 +5299,22 @@
         <v>3009.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>2912.716653329983</v>
+        <v>2670.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>2510.472919442497</v>
+        <v>2268.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>2127.795117253786</v>
+        <v>1885.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>1736.508777879091</v>
+        <v>1494.414599770435</v>
       </c>
       <c r="X14" t="n">
-        <v>1391.779653171346</v>
+        <v>1149.68547506269</v>
       </c>
       <c r="Y14" t="n">
-        <v>1128.832751471542</v>
+        <v>886.7385733628859</v>
       </c>
     </row>
     <row r="15">
@@ -5345,28 +5345,28 @@
         <v>65.12</v>
       </c>
       <c r="I15" t="n">
-        <v>98.65487796756496</v>
+        <v>65.12</v>
       </c>
       <c r="J15" t="n">
-        <v>222.6113981428639</v>
+        <v>437.5665201752989</v>
       </c>
       <c r="K15" t="n">
-        <v>411.8042142372473</v>
+        <v>626.7593362696823</v>
       </c>
       <c r="L15" t="n">
-        <v>931.6446758324474</v>
+        <v>924.8325119997294</v>
       </c>
       <c r="M15" t="n">
-        <v>1266.215217575307</v>
+        <v>1259.403053742589</v>
       </c>
       <c r="N15" t="n">
-        <v>1647.985502182875</v>
+        <v>1641.173338350157</v>
       </c>
       <c r="O15" t="n">
-        <v>1887.027953866594</v>
+        <v>2128.705790033876</v>
       </c>
       <c r="P15" t="n">
-        <v>2164.093606942957</v>
+        <v>2241.235134503383</v>
       </c>
       <c r="Q15" t="n">
         <v>2241.235134503383</v>
@@ -5412,37 +5412,37 @@
         <v>283.9399739669084</v>
       </c>
       <c r="E16" t="n">
-        <v>253.6562317073563</v>
+        <v>283.9399739669084</v>
       </c>
       <c r="F16" t="n">
-        <v>230.0371852752938</v>
+        <v>283.9399739669084</v>
       </c>
       <c r="G16" t="n">
-        <v>235.933751162179</v>
+        <v>289.8365398537936</v>
       </c>
       <c r="H16" t="n">
-        <v>257.9403363215766</v>
+        <v>311.8431250131912</v>
       </c>
       <c r="I16" t="n">
-        <v>331.5632152576595</v>
+        <v>385.4660039492741</v>
       </c>
       <c r="J16" t="n">
-        <v>545.1369559101108</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="K16" t="n">
-        <v>544.7556226521192</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="L16" t="n">
-        <v>544.7556226521192</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="M16" t="n">
-        <v>544.7556226521192</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="N16" t="n">
-        <v>544.7556226521192</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="O16" t="n">
-        <v>544.7556226521192</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="P16" t="n">
         <v>544.7556226521192</v>
@@ -5491,7 +5491,7 @@
         <v>574.8062027180183</v>
       </c>
       <c r="E17" t="n">
-        <v>448.6115754530863</v>
+        <v>448.1766172565348</v>
       </c>
       <c r="F17" t="n">
         <v>321.4503343338824</v>
@@ -5512,19 +5512,19 @@
         <v>1166.135479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>1326.070851496302</v>
+        <v>1205.680904947332</v>
       </c>
       <c r="M17" t="n">
-        <v>1836.919680225237</v>
+        <v>1205.680904947332</v>
       </c>
       <c r="N17" t="n">
-        <v>2450.14</v>
+        <v>1205.680904947332</v>
       </c>
       <c r="O17" t="n">
-        <v>3256</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>3256</v>
@@ -5585,25 +5585,25 @@
         <v>65.12</v>
       </c>
       <c r="J18" t="n">
-        <v>189.076520175299</v>
+        <v>465.2865201752989</v>
       </c>
       <c r="K18" t="n">
-        <v>378.2693362696824</v>
+        <v>930.6893362696824</v>
       </c>
       <c r="L18" t="n">
-        <v>649.6197978648825</v>
+        <v>1202.039797864883</v>
       </c>
       <c r="M18" t="n">
-        <v>1011.910339607742</v>
+        <v>1288.120339607742</v>
       </c>
       <c r="N18" t="n">
-        <v>1145.19062421531</v>
+        <v>1465.420914107732</v>
       </c>
       <c r="O18" t="n">
-        <v>1599.601838231026</v>
+        <v>1704.463365791451</v>
       </c>
       <c r="P18" t="n">
-        <v>1712.131182700533</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q18" t="n">
         <v>1816.992710260958</v>
@@ -5667,25 +5667,25 @@
         <v>859.3027230120967</v>
       </c>
       <c r="K19" t="n">
-        <v>849.6857797786189</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="L19" t="n">
-        <v>849.6857797786189</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="M19" t="n">
-        <v>849.6857797786189</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="N19" t="n">
-        <v>849.6857797786189</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O19" t="n">
-        <v>484.5892504058765</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P19" t="n">
-        <v>484.5892504058765</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="Q19" t="n">
-        <v>484.5892504058765</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R19" t="n">
         <v>65.12</v>
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>879.6685602764463</v>
+        <v>879.6685602765009</v>
       </c>
       <c r="C20" t="n">
-        <v>707.4720165966545</v>
+        <v>707.4720165967091</v>
       </c>
       <c r="D20" t="n">
-        <v>574.8062027180183</v>
+        <v>574.8062027180729</v>
       </c>
       <c r="E20" t="n">
-        <v>448.1766172565348</v>
+        <v>448.1766172565894</v>
       </c>
       <c r="F20" t="n">
-        <v>321.4503343338824</v>
+        <v>321.0153761373855</v>
       </c>
       <c r="G20" t="n">
-        <v>195.4327865692196</v>
+        <v>194.9978283727226</v>
       </c>
       <c r="H20" t="n">
         <v>65.12</v>
@@ -5746,19 +5746,19 @@
         <v>65.12</v>
       </c>
       <c r="K20" t="n">
-        <v>774.8263663478684</v>
+        <v>694.8320762183973</v>
       </c>
       <c r="L20" t="n">
-        <v>1580.686366347868</v>
+        <v>1500.692076218397</v>
       </c>
       <c r="M20" t="n">
-        <v>2091.535195076804</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="N20" t="n">
-        <v>2704.755514851567</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O20" t="n">
-        <v>2704.755514851567</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P20" t="n">
         <v>2817.400904947332</v>
@@ -5767,28 +5767,28 @@
         <v>3256</v>
       </c>
       <c r="R20" t="n">
-        <v>3256</v>
+        <v>3256.000000000055</v>
       </c>
       <c r="S20" t="n">
-        <v>3037.971547674421</v>
+        <v>3037.971547674476</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.188131787037</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.22722618238</v>
       </c>
       <c r="V20" t="n">
-        <v>1998.832252276443</v>
+        <v>1998.832252276497</v>
       </c>
       <c r="W20" t="n">
-        <v>1635.828741184576</v>
+        <v>1635.828741184631</v>
       </c>
       <c r="X20" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.382444759714</v>
       </c>
       <c r="Y20" t="n">
-        <v>1084.718371342683</v>
+        <v>1084.718371342738</v>
       </c>
     </row>
     <row r="21">
@@ -5822,25 +5822,25 @@
         <v>65.12</v>
       </c>
       <c r="J21" t="n">
-        <v>404.4452825072959</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K21" t="n">
-        <v>593.6380986016793</v>
+        <v>654.4793362696823</v>
       </c>
       <c r="L21" t="n">
-        <v>1141.198560196879</v>
+        <v>925.8297978648825</v>
       </c>
       <c r="M21" t="n">
-        <v>1227.279101939739</v>
+        <v>1011.910339607742</v>
       </c>
       <c r="N21" t="n">
-        <v>1360.559386547307</v>
+        <v>1145.19062421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1599.601838231026</v>
+        <v>1660.443075899029</v>
       </c>
       <c r="P21" t="n">
-        <v>1712.131182700533</v>
+        <v>1772.972420368535</v>
       </c>
       <c r="Q21" t="n">
         <v>1816.992710260958</v>
@@ -5877,55 +5877,55 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>414.3442160506673</v>
+        <v>422.5399739669084</v>
       </c>
       <c r="C22" t="n">
-        <v>420.5562218691031</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="D22" t="n">
-        <v>420.5562218691031</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="E22" t="n">
-        <v>420.5562218691031</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="F22" t="n">
-        <v>425.1271944610386</v>
+        <v>433.3229523772797</v>
       </c>
       <c r="G22" t="n">
-        <v>458.7437603479239</v>
+        <v>466.939518264165</v>
       </c>
       <c r="H22" t="n">
-        <v>508.4703455073215</v>
+        <v>516.6661034235625</v>
       </c>
       <c r="I22" t="n">
-        <v>609.8132244434044</v>
+        <v>618.0089823596454</v>
       </c>
       <c r="J22" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="K22" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="L22" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="M22" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="N22" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O22" t="n">
-        <v>851.1069650958557</v>
+        <v>516.472794369291</v>
       </c>
       <c r="P22" t="n">
-        <v>438.5333314309289</v>
+        <v>516.472794369291</v>
       </c>
       <c r="Q22" t="n">
-        <v>149.3356360634903</v>
+        <v>65.12</v>
       </c>
       <c r="R22" t="n">
-        <v>149.3356360634903</v>
+        <v>65.12</v>
       </c>
       <c r="S22" t="n">
         <v>65.12</v>
@@ -5986,10 +5986,10 @@
         <v>1166.135479385524</v>
       </c>
       <c r="L23" t="n">
-        <v>1166.135479385524</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M23" t="n">
-        <v>1676.984308114459</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="N23" t="n">
         <v>2011.540904947332</v>
@@ -6056,25 +6056,25 @@
         <v>65.12</v>
       </c>
       <c r="I24" t="n">
-        <v>126.374877967565</v>
+        <v>65.12</v>
       </c>
       <c r="J24" t="n">
-        <v>526.5413981428638</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>974.7096261621045</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L24" t="n">
-        <v>1246.060087757305</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M24" t="n">
-        <v>1332.140629500164</v>
+        <v>735.7003396077417</v>
       </c>
       <c r="N24" t="n">
-        <v>1465.420914107732</v>
+        <v>913.0009141077322</v>
       </c>
       <c r="O24" t="n">
-        <v>1704.463365791451</v>
+        <v>1428.253365791451</v>
       </c>
       <c r="P24" t="n">
         <v>1816.992710260958</v>
@@ -6156,10 +6156,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="P25" t="n">
-        <v>859.3027230120967</v>
+        <v>446.72908934717</v>
       </c>
       <c r="Q25" t="n">
-        <v>517.2433615971223</v>
+        <v>446.72908934717</v>
       </c>
       <c r="R25" t="n">
         <v>65.12</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>423.5780423170554</v>
+        <v>841.8265477709492</v>
       </c>
       <c r="C26" t="n">
-        <v>423.5780423170554</v>
+        <v>615.0845495457029</v>
       </c>
       <c r="D26" t="n">
-        <v>423.5780423170554</v>
+        <v>427.8732811216122</v>
       </c>
       <c r="E26" t="n">
-        <v>242.4030023101174</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="F26" t="n">
-        <v>242.4030023101174</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="G26" t="n">
-        <v>61.84</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6220,19 +6220,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>764.0617564436343</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L26" t="n">
-        <v>1529.331756443634</v>
+        <v>1218.419113037656</v>
       </c>
       <c r="M26" t="n">
-        <v>2040.180585172569</v>
+        <v>1274.910585172543</v>
       </c>
       <c r="N26" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947306</v>
       </c>
       <c r="O26" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947306</v>
       </c>
       <c r="P26" t="n">
         <v>2653.400904947332</v>
@@ -6247,22 +6247,22 @@
         <v>2793.286094312508</v>
       </c>
       <c r="T26" t="n">
-        <v>2427.957223879615</v>
+        <v>2588.112486404101</v>
       </c>
       <c r="U26" t="n">
-        <v>1999.450863729503</v>
+        <v>2588.112486404101</v>
       </c>
       <c r="V26" t="n">
-        <v>1590.510435278166</v>
+        <v>2179.172057952764</v>
       </c>
       <c r="W26" t="n">
-        <v>1172.961469640845</v>
+        <v>1761.623092315443</v>
       </c>
       <c r="X26" t="n">
-        <v>801.9697186704736</v>
+        <v>1390.631341345071</v>
       </c>
       <c r="Y26" t="n">
-        <v>683.1733079287469</v>
+        <v>1101.421813382641</v>
       </c>
     </row>
     <row r="27">
@@ -6296,25 +6296,25 @@
         <v>61.84</v>
       </c>
       <c r="J27" t="n">
-        <v>263.9186282495398</v>
+        <v>408.546520175299</v>
       </c>
       <c r="K27" t="n">
-        <v>675.8614443439233</v>
+        <v>820.4893362696823</v>
       </c>
       <c r="L27" t="n">
-        <v>1169.961905939123</v>
+        <v>1314.589797864882</v>
       </c>
       <c r="M27" t="n">
-        <v>1478.792447681983</v>
+        <v>1427.390920121557</v>
       </c>
       <c r="N27" t="n">
-        <v>1834.822732289551</v>
+        <v>1783.421204729126</v>
       </c>
       <c r="O27" t="n">
-        <v>2296.61518397327</v>
+        <v>2245.213656412845</v>
       </c>
       <c r="P27" t="n">
-        <v>2631.894528442776</v>
+        <v>2580.493000882351</v>
       </c>
       <c r="Q27" t="n">
         <v>2631.894528442776</v>
@@ -6351,22 +6351,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>224.8859058312735</v>
+        <v>179.5340635277899</v>
       </c>
       <c r="C28" t="n">
-        <v>176.6785859847637</v>
+        <v>179.5340635277899</v>
       </c>
       <c r="D28" t="n">
-        <v>115.5308909791521</v>
+        <v>118.3863685221783</v>
       </c>
       <c r="E28" t="n">
-        <v>115.5308909791521</v>
+        <v>61.84</v>
       </c>
       <c r="F28" t="n">
-        <v>65.64921828446326</v>
+        <v>61.84</v>
       </c>
       <c r="G28" t="n">
-        <v>65.64921828446326</v>
+        <v>61.84</v>
       </c>
       <c r="H28" t="n">
         <v>61.84</v>
@@ -6387,40 +6387,40 @@
         <v>233.3942218096018</v>
       </c>
       <c r="N28" t="n">
-        <v>174.283957157794</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="O28" t="n">
-        <v>174.283957157794</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="P28" t="n">
-        <v>174.283957157794</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="Q28" t="n">
-        <v>174.283957157794</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="R28" t="n">
-        <v>174.283957157794</v>
+        <v>233.3942218096018</v>
       </c>
       <c r="S28" t="n">
-        <v>174.283957157794</v>
+        <v>151.602463773611</v>
       </c>
       <c r="T28" t="n">
-        <v>189.1096363165988</v>
+        <v>166.4281429324158</v>
       </c>
       <c r="U28" t="n">
-        <v>262.4108289548855</v>
+        <v>239.7293355707025</v>
       </c>
       <c r="V28" t="n">
-        <v>287.9822218408314</v>
+        <v>265.3007284566484</v>
       </c>
       <c r="W28" t="n">
-        <v>287.9822218408314</v>
+        <v>265.3007284566484</v>
       </c>
       <c r="X28" t="n">
-        <v>287.9822218408314</v>
+        <v>242.6303795373479</v>
       </c>
       <c r="Y28" t="n">
-        <v>224.8859058312735</v>
+        <v>179.5340635277899</v>
       </c>
     </row>
     <row r="29">
@@ -6454,25 +6454,25 @@
         <v>61.84</v>
       </c>
       <c r="J29" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K29" t="n">
-        <v>764.0617564436008</v>
+        <v>61.84</v>
       </c>
       <c r="L29" t="n">
-        <v>764.0617564436008</v>
+        <v>61.84</v>
       </c>
       <c r="M29" t="n">
-        <v>1274.910585172536</v>
+        <v>572.6888287289351</v>
       </c>
       <c r="N29" t="n">
-        <v>1888.130904947299</v>
+        <v>1185.909148503698</v>
       </c>
       <c r="O29" t="n">
-        <v>1888.130904947299</v>
+        <v>1951.179148503732</v>
       </c>
       <c r="P29" t="n">
-        <v>2653.400904947332</v>
+        <v>2716.449148503766</v>
       </c>
       <c r="Q29" t="n">
         <v>3092</v>
@@ -6481,25 +6481,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>3056.115789200078</v>
+        <v>2793.286094312508</v>
       </c>
       <c r="T29" t="n">
-        <v>2690.786918767185</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>2690.786918767185</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="V29" t="n">
-        <v>2281.846490315848</v>
+        <v>2019.016795428278</v>
       </c>
       <c r="W29" t="n">
-        <v>1864.297524678527</v>
+        <v>1601.467829790957</v>
       </c>
       <c r="X29" t="n">
-        <v>1493.305773708156</v>
+        <v>1601.467829790957</v>
       </c>
       <c r="Y29" t="n">
-        <v>1204.096245745725</v>
+        <v>1463.691511357417</v>
       </c>
     </row>
     <row r="30">
@@ -6594,37 +6594,37 @@
         <v>175.5382646830375</v>
       </c>
       <c r="D31" t="n">
-        <v>175.5382646830375</v>
+        <v>114.3905696774259</v>
       </c>
       <c r="E31" t="n">
-        <v>175.5382646830375</v>
+        <v>114.3905696774259</v>
       </c>
       <c r="F31" t="n">
-        <v>175.5382646830375</v>
+        <v>114.3905696774259</v>
       </c>
       <c r="G31" t="n">
-        <v>175.5382646830375</v>
+        <v>114.3905696774259</v>
       </c>
       <c r="H31" t="n">
-        <v>175.5382646830375</v>
+        <v>110.5813513929626</v>
       </c>
       <c r="I31" t="n">
-        <v>223.4211436191204</v>
+        <v>158.4642303290455</v>
       </c>
       <c r="J31" t="n">
-        <v>411.2548842715717</v>
+        <v>346.2979709814969</v>
       </c>
       <c r="K31" t="n">
-        <v>411.2548842715717</v>
+        <v>346.2979709814969</v>
       </c>
       <c r="L31" t="n">
-        <v>411.2548842715717</v>
+        <v>346.2979709814969</v>
       </c>
       <c r="M31" t="n">
-        <v>411.2548842715717</v>
+        <v>346.2979709814969</v>
       </c>
       <c r="N31" t="n">
-        <v>411.2548842715717</v>
+        <v>61.84</v>
       </c>
       <c r="O31" t="n">
         <v>61.84</v>
@@ -6667,25 +6667,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C32" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D32" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E32" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F32" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G32" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H32" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I32" t="n">
         <v>61.84</v>
@@ -6694,49 +6694,49 @@
         <v>445.5561922637026</v>
       </c>
       <c r="K32" t="n">
-        <v>430.0181114556216</v>
+        <v>1155.056868702876</v>
       </c>
       <c r="L32" t="n">
-        <v>414.4800306475407</v>
+        <v>1920.326868702876</v>
       </c>
       <c r="M32" t="n">
-        <v>518.4380752395892</v>
+        <v>2357.806161616123</v>
       </c>
       <c r="N32" t="n">
-        <v>1129.493647533164</v>
+        <v>2342.268080808041</v>
       </c>
       <c r="O32" t="n">
-        <v>1894.763647533204</v>
+        <v>2326.72999999996</v>
       </c>
       <c r="P32" t="n">
-        <v>2660.033647533245</v>
+        <v>3092</v>
       </c>
       <c r="Q32" t="n">
         <v>3092</v>
       </c>
       <c r="R32" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S32" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T32" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U32" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V32" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W32" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X32" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y32" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="33">
@@ -6767,16 +6767,16 @@
         <v>61.84</v>
       </c>
       <c r="I33" t="n">
-        <v>134.974877967565</v>
+        <v>61.84</v>
       </c>
       <c r="J33" t="n">
-        <v>547.0213981428639</v>
+        <v>185.796520175299</v>
       </c>
       <c r="K33" t="n">
-        <v>736.2142142372472</v>
+        <v>374.9893362696823</v>
       </c>
       <c r="L33" t="n">
-        <v>1007.564675832447</v>
+        <v>772.8719059391233</v>
       </c>
       <c r="M33" t="n">
         <v>1147.042447681983</v>
@@ -6837,40 +6837,40 @@
         <v>519.4266664670818</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590409</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459262</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053238</v>
       </c>
       <c r="I34" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414067</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693858</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="L34" t="n">
-        <v>1011.831843630703</v>
+        <v>877.9453505420606</v>
       </c>
       <c r="M34" t="n">
-        <v>1011.831843630703</v>
+        <v>645.9942279132224</v>
       </c>
       <c r="N34" t="n">
-        <v>901.5240037917935</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="O34" t="n">
-        <v>901.5240037917935</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="P34" t="n">
-        <v>501.0715822480788</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.84</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R34" t="n">
         <v>61.84</v>
@@ -6928,25 +6928,25 @@
         <v>61.84</v>
       </c>
       <c r="J35" t="n">
-        <v>61.84</v>
+        <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>61.84</v>
+        <v>1155.056868702876</v>
       </c>
       <c r="L35" t="n">
-        <v>827.1099999999999</v>
+        <v>1139.518787894795</v>
       </c>
       <c r="M35" t="n">
-        <v>1332.793048391934</v>
+        <v>1645.201836286729</v>
       </c>
       <c r="N35" t="n">
-        <v>1561.459999999904</v>
+        <v>2255.334931659408</v>
       </c>
       <c r="O35" t="n">
-        <v>2326.729999999952</v>
+        <v>3020.604931659455</v>
       </c>
       <c r="P35" t="n">
-        <v>3092</v>
+        <v>3005.066850851374</v>
       </c>
       <c r="Q35" t="n">
         <v>3092</v>
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>368.1567292570302</v>
+        <v>1828.262200814254</v>
       </c>
       <c r="C36" t="n">
-        <v>297.3487368878188</v>
+        <v>1757.454208445042</v>
       </c>
       <c r="D36" t="n">
-        <v>239.8359218396343</v>
+        <v>1699.941393396858</v>
       </c>
       <c r="E36" t="n">
-        <v>187.6418842417428</v>
+        <v>1647.747355798967</v>
       </c>
       <c r="F36" t="n">
-        <v>138.5143667287359</v>
+        <v>1598.61983828596</v>
       </c>
       <c r="G36" t="n">
-        <v>103.4239264509305</v>
+        <v>1563.529398008154</v>
       </c>
       <c r="H36" t="n">
-        <v>61.84</v>
+        <v>1521.945471557224</v>
       </c>
       <c r="I36" t="n">
-        <v>61.84</v>
+        <v>1595.080349524789</v>
       </c>
       <c r="J36" t="n">
-        <v>185.796520175299</v>
+        <v>2007.126869700088</v>
       </c>
       <c r="K36" t="n">
-        <v>374.9893362696823</v>
+        <v>2196.319685794471</v>
       </c>
       <c r="L36" t="n">
-        <v>646.3397978648825</v>
+        <v>2467.670147389671</v>
       </c>
       <c r="M36" t="n">
-        <v>732.4203396077418</v>
+        <v>2553.75068913253</v>
       </c>
       <c r="N36" t="n">
-        <v>865.7006242153101</v>
+        <v>2687.030973740098</v>
       </c>
       <c r="O36" t="n">
-        <v>1231.27518397327</v>
+        <v>2926.073425423817</v>
       </c>
       <c r="P36" t="n">
-        <v>1631.894528442776</v>
+        <v>3038.602769893324</v>
       </c>
       <c r="Q36" t="n">
-        <v>1631.894528442776</v>
+        <v>3092</v>
       </c>
       <c r="R36" t="n">
-        <v>1373.032106935323</v>
+        <v>2833.137578492546</v>
       </c>
       <c r="S36" t="n">
-        <v>1195.694733233695</v>
+        <v>2655.800204790919</v>
       </c>
       <c r="T36" t="n">
-        <v>1080.18183907459</v>
+        <v>2540.287310631814</v>
       </c>
       <c r="U36" t="n">
-        <v>969.8683443673306</v>
+        <v>2429.973815924554</v>
       </c>
       <c r="V36" t="n">
-        <v>845.1100946789263</v>
+        <v>2305.21556623615</v>
       </c>
       <c r="W36" t="n">
-        <v>702.308940224554</v>
+        <v>2162.414411781778</v>
       </c>
       <c r="X36" t="n">
-        <v>572.1445569463848</v>
+        <v>2032.250028503609</v>
       </c>
       <c r="Y36" t="n">
-        <v>462.6583016270571</v>
+        <v>1922.763773184281</v>
       </c>
     </row>
     <row r="37">
@@ -7092,25 +7092,25 @@
         <v>1011.831843630726</v>
       </c>
       <c r="L37" t="n">
-        <v>877.9453505420606</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="M37" t="n">
-        <v>877.9453505420606</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="N37" t="n">
-        <v>877.9453505420606</v>
+        <v>728.8166160835699</v>
       </c>
       <c r="O37" t="n">
-        <v>877.9453505420606</v>
+        <v>375.8412988320396</v>
       </c>
       <c r="P37" t="n">
-        <v>573.1660061903571</v>
+        <v>375.8412988320396</v>
       </c>
       <c r="Q37" t="n">
-        <v>133.9344239422782</v>
+        <v>61.84</v>
       </c>
       <c r="R37" t="n">
-        <v>133.9344239422782</v>
+        <v>61.84</v>
       </c>
       <c r="S37" t="n">
         <v>61.84</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C38" t="n">
         <v>644.0209141871454</v>
@@ -7168,16 +7168,16 @@
         <v>445.5561922637023</v>
       </c>
       <c r="K38" t="n">
-        <v>810.0236653847415</v>
+        <v>430.0181114556214</v>
       </c>
       <c r="L38" t="n">
-        <v>794.4855845766606</v>
+        <v>415.4025075684321</v>
       </c>
       <c r="M38" t="n">
-        <v>1300.168632968594</v>
+        <v>921.0855559603656</v>
       </c>
       <c r="N38" t="n">
-        <v>1910.301728341273</v>
+        <v>1129.493647533136</v>
       </c>
       <c r="O38" t="n">
         <v>1894.763647533191</v>
@@ -7189,28 +7189,28 @@
         <v>3092</v>
       </c>
       <c r="R38" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S38" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T38" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U38" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V38" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W38" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X38" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y38" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="39">
@@ -7241,16 +7241,16 @@
         <v>61.84</v>
       </c>
       <c r="I39" t="n">
-        <v>61.84</v>
+        <v>134.974877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>473.8865201752989</v>
+        <v>312.3286282495397</v>
       </c>
       <c r="K39" t="n">
-        <v>663.0793362696822</v>
+        <v>501.5214443439232</v>
       </c>
       <c r="L39" t="n">
-        <v>1060.961905939123</v>
+        <v>772.8719059391233</v>
       </c>
       <c r="M39" t="n">
         <v>1147.042447681983</v>
@@ -7329,25 +7329,25 @@
         <v>1011.83184363073</v>
       </c>
       <c r="L40" t="n">
-        <v>877.9453505420643</v>
+        <v>1011.83184363073</v>
       </c>
       <c r="M40" t="n">
-        <v>877.9453505420643</v>
+        <v>856.1812337375136</v>
       </c>
       <c r="N40" t="n">
-        <v>877.9453505420643</v>
+        <v>573.1660061903571</v>
       </c>
       <c r="O40" t="n">
-        <v>524.970033290534</v>
+        <v>573.1660061903571</v>
       </c>
       <c r="P40" t="n">
-        <v>501.0715822480788</v>
+        <v>573.1660061903571</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="R40" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="S40" t="n">
         <v>61.84</v>
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>690.3668780136743</v>
+        <v>645.943613149907</v>
       </c>
       <c r="C41" t="n">
-        <v>451.5036676672158</v>
+        <v>645.943613149907</v>
       </c>
       <c r="D41" t="n">
-        <v>451.5036676672158</v>
+        <v>645.943613149907</v>
       </c>
       <c r="E41" t="n">
-        <v>451.5036676672158</v>
+        <v>452.6473610217569</v>
       </c>
       <c r="F41" t="n">
-        <v>451.5036676672158</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="G41" t="n">
         <v>258.8194532358863</v>
@@ -7402,25 +7402,25 @@
         <v>61.84</v>
       </c>
       <c r="J41" t="n">
-        <v>61.84</v>
+        <v>437.3908514962396</v>
       </c>
       <c r="K41" t="n">
-        <v>771.5463663478683</v>
+        <v>437.3908514962396</v>
       </c>
       <c r="L41" t="n">
-        <v>1536.816366347868</v>
+        <v>1202.66085149624</v>
       </c>
       <c r="M41" t="n">
-        <v>1536.816366347868</v>
+        <v>1713.509680225175</v>
       </c>
       <c r="N41" t="n">
-        <v>1536.816366347868</v>
+        <v>2326.729999999938</v>
       </c>
       <c r="O41" t="n">
-        <v>1888.13090494727</v>
+        <v>3092</v>
       </c>
       <c r="P41" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q41" t="n">
         <v>3092</v>
@@ -7429,25 +7429,25 @@
         <v>3092</v>
       </c>
       <c r="S41" t="n">
-        <v>2807.304881007754</v>
+        <v>3092</v>
       </c>
       <c r="T41" t="n">
-        <v>2429.854798453649</v>
+        <v>2714.549917445895</v>
       </c>
       <c r="U41" t="n">
-        <v>2067.588699494353</v>
+        <v>2452.835612389119</v>
       </c>
       <c r="V41" t="n">
-        <v>1646.527058921804</v>
+        <v>2031.77397181657</v>
       </c>
       <c r="W41" t="n">
-        <v>1646.527058921804</v>
+        <v>1602.103794058037</v>
       </c>
       <c r="X41" t="n">
-        <v>1263.414095830221</v>
+        <v>1218.990830966453</v>
       </c>
       <c r="Y41" t="n">
-        <v>962.0833557465778</v>
+        <v>917.6600908828107</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>840.8840019843029</v>
+        <v>845.0520685412207</v>
       </c>
       <c r="C42" t="n">
-        <v>691.2881308272127</v>
+        <v>695.4561973841305</v>
       </c>
       <c r="D42" t="n">
-        <v>554.9874369911495</v>
+        <v>559.1555035480673</v>
       </c>
       <c r="E42" t="n">
-        <v>424.0055206053792</v>
+        <v>428.1735871622969</v>
       </c>
       <c r="F42" t="n">
-        <v>296.0901243044934</v>
+        <v>300.2581908614112</v>
       </c>
       <c r="G42" t="n">
-        <v>182.2118052388092</v>
+        <v>186.379871795727</v>
       </c>
       <c r="H42" t="n">
-        <v>61.84</v>
+        <v>66.00806655691771</v>
       </c>
       <c r="I42" t="n">
         <v>61.84</v>
@@ -7496,10 +7496,10 @@
         <v>1920.05062421531</v>
       </c>
       <c r="O42" t="n">
-        <v>2168.608743171805</v>
+        <v>2369.963075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>2492.008087641312</v>
+        <v>2531.529615201737</v>
       </c>
       <c r="Q42" t="n">
         <v>2531.529615201737</v>
@@ -7508,25 +7508,25 @@
         <v>2193.879314906404</v>
       </c>
       <c r="S42" t="n">
-        <v>2025.636384529135</v>
+        <v>1937.754062416898</v>
       </c>
       <c r="T42" t="n">
-        <v>2025.636384529135</v>
+        <v>1743.453289469915</v>
       </c>
       <c r="U42" t="n">
-        <v>1836.535011033997</v>
+        <v>1554.351915974776</v>
       </c>
       <c r="V42" t="n">
-        <v>1632.988882557714</v>
+        <v>1554.351915974776</v>
       </c>
       <c r="W42" t="n">
-        <v>1411.399849315463</v>
+        <v>1332.762882732525</v>
       </c>
       <c r="X42" t="n">
-        <v>1202.447587249415</v>
+        <v>1206.615653806333</v>
       </c>
       <c r="Y42" t="n">
-        <v>1014.173453142209</v>
+        <v>1018.341519699126</v>
       </c>
     </row>
     <row r="43">
@@ -7548,40 +7548,40 @@
         <v>139.8982646830375</v>
       </c>
       <c r="F43" t="n">
-        <v>139.8982646830375</v>
+        <v>77.89537986713651</v>
       </c>
       <c r="G43" t="n">
-        <v>139.8982646830375</v>
+        <v>77.89537986713651</v>
       </c>
       <c r="H43" t="n">
-        <v>139.8982646830375</v>
+        <v>77.89537986713651</v>
       </c>
       <c r="I43" t="n">
-        <v>175.9011436191204</v>
+        <v>113.8982588032194</v>
       </c>
       <c r="J43" t="n">
-        <v>351.8548842715717</v>
+        <v>289.8519994556707</v>
       </c>
       <c r="K43" t="n">
-        <v>351.8548842715717</v>
+        <v>289.8519994556707</v>
       </c>
       <c r="L43" t="n">
-        <v>351.8548842715717</v>
+        <v>289.8519994556707</v>
       </c>
       <c r="M43" t="n">
-        <v>351.8548842715717</v>
+        <v>289.8519994556707</v>
       </c>
       <c r="N43" t="n">
-        <v>351.8548842715717</v>
+        <v>289.8519994556707</v>
       </c>
       <c r="O43" t="n">
-        <v>351.8548842715717</v>
+        <v>61.84</v>
       </c>
       <c r="P43" t="n">
-        <v>351.8548842715717</v>
+        <v>61.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>351.8548842715717</v>
+        <v>61.84</v>
       </c>
       <c r="R43" t="n">
         <v>61.84</v>
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1215.452435354799</v>
+        <v>1214.840397657979</v>
       </c>
       <c r="C44" t="n">
-        <v>950.3265987457148</v>
+        <v>949.7145610488942</v>
       </c>
       <c r="D44" t="n">
-        <v>724.7314919377858</v>
+        <v>724.1194542409652</v>
       </c>
       <c r="E44" t="n">
-        <v>505.1726135470094</v>
+        <v>724.1194542409652</v>
       </c>
       <c r="F44" t="n">
-        <v>285.0820794985125</v>
+        <v>504.0289201924683</v>
       </c>
       <c r="G44" t="n">
         <v>285.0820794985125</v>
@@ -7645,46 +7645,46 @@
         <v>771.5463663478683</v>
       </c>
       <c r="L44" t="n">
-        <v>1536.816366347868</v>
+        <v>1529.331756443634</v>
       </c>
       <c r="M44" t="n">
-        <v>2047.665195076803</v>
+        <v>2040.180585172569</v>
       </c>
       <c r="N44" t="n">
-        <v>2660.885514851566</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>2660.885514851566</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2660.885514851566</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>3092</v>
       </c>
       <c r="R44" t="n">
-        <v>3092</v>
+        <v>3027.476162799703</v>
       </c>
       <c r="S44" t="n">
-        <v>2781.042254745129</v>
+        <v>2716.518417544831</v>
       </c>
       <c r="T44" t="n">
-        <v>2763.847908251708</v>
+        <v>2312.8057087281</v>
       </c>
       <c r="U44" t="n">
-        <v>2296.957709717758</v>
+        <v>2312.8057087281</v>
       </c>
       <c r="V44" t="n">
-        <v>2296.957709717758</v>
+        <v>2296.345672020937</v>
       </c>
       <c r="W44" t="n">
-        <v>1841.024905696598</v>
+        <v>1840.412867999778</v>
       </c>
       <c r="X44" t="n">
-        <v>1841.024905696598</v>
+        <v>1840.412867999778</v>
       </c>
       <c r="Y44" t="n">
-        <v>1513.431539350329</v>
+        <v>1512.819501653509</v>
       </c>
     </row>
     <row r="45">
@@ -7694,13 +7694,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>866.3271322809151</v>
+        <v>871.6459097312079</v>
       </c>
       <c r="C45" t="n">
-        <v>690.4686348611986</v>
+        <v>695.7874123114914</v>
       </c>
       <c r="D45" t="n">
-        <v>690.4686348611986</v>
+        <v>533.2240922128019</v>
       </c>
       <c r="E45" t="n">
         <v>533.2240922128019</v>
@@ -7718,52 +7718,52 @@
         <v>61.84</v>
       </c>
       <c r="J45" t="n">
-        <v>351.0409868458581</v>
+        <v>370.9265201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>725.3638029402416</v>
+        <v>745.2493362696823</v>
       </c>
       <c r="L45" t="n">
-        <v>996.7142645354418</v>
+        <v>1016.599797864882</v>
       </c>
       <c r="M45" t="n">
-        <v>1267.924806278301</v>
+        <v>1287.810339607742</v>
       </c>
       <c r="N45" t="n">
-        <v>1586.335090885869</v>
+        <v>1606.22062421531</v>
       </c>
       <c r="O45" t="n">
-        <v>2010.507542569588</v>
+        <v>2030.393075899029</v>
       </c>
       <c r="P45" t="n">
-        <v>2308.166887039095</v>
+        <v>2302.357710282822</v>
       </c>
       <c r="Q45" t="n">
-        <v>2321.94841459952</v>
+        <v>2316.139237843247</v>
       </c>
       <c r="R45" t="n">
-        <v>2321.94841459952</v>
+        <v>2316.139237843247</v>
       </c>
       <c r="S45" t="n">
-        <v>2039.560535847388</v>
+        <v>2219.173449303643</v>
       </c>
       <c r="T45" t="n">
-        <v>1818.997136637778</v>
+        <v>1998.610050094033</v>
       </c>
       <c r="U45" t="n">
-        <v>1603.633136880013</v>
+        <v>1998.610050094033</v>
       </c>
       <c r="V45" t="n">
-        <v>1603.633136880013</v>
+        <v>1768.801295355124</v>
       </c>
       <c r="W45" t="n">
-        <v>1515.630858399954</v>
+        <v>1520.949635850247</v>
       </c>
       <c r="X45" t="n">
-        <v>1280.41597007128</v>
+        <v>1285.734747521572</v>
       </c>
       <c r="Y45" t="n">
-        <v>1065.879209701447</v>
+        <v>1071.19798715174</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>61.84</v>
+        <v>192.2985677468288</v>
       </c>
       <c r="C46" t="n">
-        <v>61.84</v>
+        <v>192.2985677468288</v>
       </c>
       <c r="D46" t="n">
-        <v>61.84</v>
+        <v>192.2985677468288</v>
       </c>
       <c r="E46" t="n">
-        <v>61.84</v>
+        <v>192.2985677468288</v>
       </c>
       <c r="F46" t="n">
-        <v>61.84</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="G46" t="n">
-        <v>61.84</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="H46" t="n">
         <v>61.84</v>
       </c>
       <c r="I46" t="n">
-        <v>61.84</v>
+        <v>72.10287893608292</v>
       </c>
       <c r="J46" t="n">
-        <v>212.0537406524513</v>
+        <v>222.3166195885343</v>
       </c>
       <c r="K46" t="n">
-        <v>212.0537406524513</v>
+        <v>222.3166195885343</v>
       </c>
       <c r="L46" t="n">
-        <v>212.0537406524513</v>
+        <v>222.3166195885343</v>
       </c>
       <c r="M46" t="n">
-        <v>212.0537406524513</v>
+        <v>222.3166195885343</v>
       </c>
       <c r="N46" t="n">
-        <v>212.0537406524513</v>
+        <v>222.3166195885343</v>
       </c>
       <c r="O46" t="n">
-        <v>212.0537406524513</v>
+        <v>219.6450279822466</v>
       </c>
       <c r="P46" t="n">
-        <v>212.0537406524513</v>
+        <v>219.6450279822466</v>
       </c>
       <c r="Q46" t="n">
-        <v>65.92932235030901</v>
+        <v>219.6450279822466</v>
       </c>
       <c r="R46" t="n">
-        <v>65.92932235030901</v>
+        <v>219.6450279822466</v>
       </c>
       <c r="S46" t="n">
-        <v>65.92932235030901</v>
+        <v>219.6450279822466</v>
       </c>
       <c r="T46" t="n">
-        <v>65.92932235030901</v>
+        <v>196.3878900971378</v>
       </c>
       <c r="U46" t="n">
-        <v>101.6105149885956</v>
+        <v>232.0690827354245</v>
       </c>
       <c r="V46" t="n">
-        <v>101.6105149885956</v>
+        <v>232.0690827354245</v>
       </c>
       <c r="W46" t="n">
-        <v>61.84</v>
+        <v>192.2985677468288</v>
       </c>
       <c r="X46" t="n">
-        <v>61.84</v>
+        <v>192.2985677468288</v>
       </c>
       <c r="Y46" t="n">
-        <v>61.84</v>
+        <v>192.2985677468288</v>
       </c>
     </row>
   </sheetData>
@@ -7964,25 +7964,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>51.24160624509022</v>
       </c>
       <c r="K2" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>70.24786957409242</v>
+        <v>233.2813807819365</v>
       </c>
       <c r="P2" t="n">
-        <v>403.6719053264119</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q2" t="n">
         <v>615.8520732695737</v>
@@ -8216,13 +8216,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>70.24786957409242</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>598.2574409074598</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q5" t="n">
-        <v>615.8520732695737</v>
+        <v>399.8224541363517</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,13 +8438,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>163.033511207844</v>
+        <v>814</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
@@ -8453,10 +8453,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2870600406814674</v>
+        <v>501.1325584305591</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8675,13 +8675,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>459.6877287841431</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>814</v>
+        <v>532.5214919778891</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8693,10 +8693,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N14" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O14" t="n">
-        <v>231.79875049407</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>435.4936646866046</v>
       </c>
       <c r="Q14" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9155,22 +9155,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>161.5508809199773</v>
+        <v>39.94487430485674</v>
       </c>
       <c r="M17" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N17" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O17" t="n">
         <v>884.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,22 +9389,22 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>636.0728042610074</v>
       </c>
       <c r="L20" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>114.0702823596368</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9629,13 +9629,13 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N23" t="n">
-        <v>815.1849144666769</v>
+        <v>517.1938323746921</v>
       </c>
       <c r="O23" t="n">
         <v>70.24786957409245</v>
@@ -9863,13 +9863,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>314.0531751575542</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>1060.271045550332</v>
+        <v>601.32422070786</v>
       </c>
       <c r="N26" t="n">
         <v>1096.663422488788</v>
@@ -9878,7 +9878,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407081</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,10 +10097,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>314.0531751575203</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10112,13 +10112,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741263</v>
       </c>
       <c r="P29" t="n">
         <v>773.2870600407153</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>552.1669787681262</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,25 +10337,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>662.5632917884461</v>
+        <v>992.7493276264324</v>
       </c>
       <c r="N32" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>843.2478695741336</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
         <v>773.2870600407226</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>188.2053843274865</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,28 +10571,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>50.42570624509119</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>14.46944784831609</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>719.0119401617272</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
         <v>843.2478695741409</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600407299</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>188.2053843274865</v>
+        <v>274.269201984627</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,7 +10811,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>375.292246238148</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10820,10 +10820,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1096.663422488788</v>
+        <v>698.9556687268787</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741481</v>
       </c>
       <c r="P38" t="n">
         <v>773.2870600407372</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>414.3873006857364</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>772.9999999999999</v>
+        <v>773</v>
       </c>
       <c r="M41" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>425.1110398765186</v>
+        <v>843.2478695741554</v>
       </c>
       <c r="P41" t="n">
-        <v>773.2870600407444</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11288,7 +11288,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>772.9999999999999</v>
+        <v>765.4397879755212</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11303,7 +11303,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>608.2918612450952</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22703,10 +22703,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>29.21007785422829</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>29.21007785422267</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>29.21007785423001</v>
+        <v>5.662449696448789</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.662449696452668</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>29.21007785423001</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23226,7 +23226,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91.14075059324986</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -23235,10 +23235,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23280,10 +23280,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>423.6622064478518</v>
       </c>
       <c r="V11" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23381,22 +23381,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E13" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>3.77112610161862</v>
@@ -23423,10 +23423,10 @@
         <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>263.3451880732566</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>500.839266425598</v>
+        <v>413.9816668969112</v>
       </c>
       <c r="R13" t="n">
         <v>501.6021279811511</v>
@@ -23450,7 +23450,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -23463,10 +23463,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>80.3340805877194</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -23514,7 +23514,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>239.6732363275696</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -23627,10 +23627,10 @@
         <v>34.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -23645,7 +23645,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>37.14325387573133</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L16" t="n">
         <v>172.5476281577792</v>
@@ -23660,7 +23660,7 @@
         <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>436.4478973282775</v>
+        <v>382.7066165981673</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -23706,10 +23706,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4306086145860064</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.4306086145859922</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -23882,7 +23882,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L19" t="n">
         <v>144.5476281577792</v>
@@ -23894,16 +23894,16 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4478973282775</v>
+        <v>69.8091295274528</v>
       </c>
       <c r="Q19" t="n">
         <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>32.32757007933333</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -23946,13 +23946,13 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4306086145859922</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.430608614531991</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -24092,7 +24092,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -24131,19 +24131,19 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>361.445564079015</v>
+        <v>22.04393472263729</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>160.5335480118338</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24371,13 +24371,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>108.2004986247733</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>69.8091295274528</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24411,10 +24411,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -24423,10 +24423,10 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24462,10 +24462,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>158.5537098992413</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>168.7089860484969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24569,22 +24569,22 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G28" t="n">
         <v>20.04387284153003</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24602,7 +24602,7 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>287.6659132663951</v>
+        <v>346.1850752716849</v>
       </c>
       <c r="O28" t="n">
         <v>415.445564079015</v>
@@ -24617,7 +24617,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S28" t="n">
-        <v>137.3734797028554</v>
+        <v>56.39963924722446</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24632,7 +24632,7 @@
         <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -24645,7 +24645,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>260.2013979386944</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24711,10 +24711,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>149.9188774336016</v>
       </c>
     </row>
     <row r="30">
@@ -24809,7 +24809,7 @@
         <v>47.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>55.98090483695654</v>
@@ -24821,7 +24821,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24839,10 +24839,10 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>346.1850752716849</v>
+        <v>64.57168400000307</v>
       </c>
       <c r="O31" t="n">
-        <v>69.52482865015895</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P31" t="n">
         <v>462.4478973282775</v>
@@ -25070,25 +25070,25 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>170.9803138311647</v>
+        <v>137.4745176187459</v>
       </c>
       <c r="O34" t="n">
         <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>71.37347970285543</v>
@@ -25307,28 +25307,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M37" t="n">
         <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>94.71634642009093</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>123.9779805818787</v>
       </c>
       <c r="R37" t="n">
         <v>435.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25544,19 +25544,19 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>229.6316114025499</v>
+        <v>75.53750760826557</v>
       </c>
       <c r="N40" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>372.7884307962468</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>435.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25596,19 +25596,19 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>197.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>191.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>191.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -25644,19 +25644,19 @@
         <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>281.8481678023229</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>77.57785857890769</v>
+        <v>177.1241345424028</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>425.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -25693,7 +25693,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>4.126385891348534</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25723,22 +25723,22 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>87.00349889111524</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>192.3577652175138</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>201.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>81.97698280845709</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -25763,7 +25763,7 @@
         <v>67.98090483695654</v>
       </c>
       <c r="F43" t="n">
-        <v>61.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>32.04387284153003</v>
@@ -25790,7 +25790,7 @@
         <v>358.1850752716849</v>
       </c>
       <c r="O43" t="n">
-        <v>427.445564079015</v>
+        <v>201.713684617901</v>
       </c>
       <c r="P43" t="n">
         <v>474.4478973282775</v>
@@ -25799,7 +25799,7 @@
         <v>512.839266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>226.4873925522951</v>
+        <v>513.6021279811511</v>
       </c>
       <c r="S43" t="n">
         <v>149.3734797028554</v>
@@ -25839,13 +25839,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>217.3632896068686</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>216.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -25878,19 +25878,19 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>63.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>382.6531787000774</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>462.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>442.8510241668239</v>
+        <v>426.5555878267325</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -25915,10 +25915,10 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>160.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>155.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -25960,19 +25960,19 @@
         <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>183.5678693104037</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>213.2103597601867</v>
       </c>
       <c r="V45" t="n">
-        <v>227.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>158.2508872145699</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26000,13 +26000,13 @@
         <v>93.98090483695654</v>
       </c>
       <c r="F46" t="n">
-        <v>87.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>58.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>41.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26027,13 +26027,13 @@
         <v>384.1850752716849</v>
       </c>
       <c r="O46" t="n">
-        <v>453.445564079015</v>
+        <v>450.8006883887902</v>
       </c>
       <c r="P46" t="n">
         <v>500.4478973282775</v>
       </c>
       <c r="Q46" t="n">
-        <v>394.1760923064771</v>
+        <v>538.839266425598</v>
       </c>
       <c r="R46" t="n">
         <v>539.6021279811511</v>
@@ -26042,7 +26042,7 @@
         <v>175.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>23.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>870168.4885039973</v>
+        <v>870168.4885039974</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1562440.287659248</v>
+        <v>1562440.287659249</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2254712.0868145</v>
+        <v>2254712.086814501</v>
       </c>
     </row>
     <row r="5">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3516777.335728328</v>
+        <v>3516777.335728329</v>
       </c>
     </row>
     <row r="7">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4857848.927566481</v>
+        <v>4857848.927566484</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5528384.723485556</v>
+        <v>5528384.723485557</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6136211.839616334</v>
+        <v>6136211.839616335</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6748561.843827919</v>
+        <v>6748561.84382792</v>
       </c>
     </row>
     <row r="12">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8773212.684180895</v>
+        <v>8773212.684180891</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9365579.39667418</v>
+        <v>9365579.396674177</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9919692.338533556</v>
+        <v>9919692.338533552</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1510411.198156912</v>
+        <v>1510411.198156913</v>
       </c>
       <c r="C2" t="n">
         <v>1510411.198156913</v>
@@ -26284,22 +26284,22 @@
         <v>1406340.4197004</v>
       </c>
       <c r="G2" t="n">
-        <v>1462987.19109617</v>
+        <v>1462987.191096171</v>
       </c>
       <c r="H2" t="n">
-        <v>1462987.19109617</v>
+        <v>1462987.191096175</v>
       </c>
       <c r="I2" t="n">
-        <v>1462987.19109617</v>
+        <v>1462987.191096171</v>
       </c>
       <c r="J2" t="n">
-        <v>1336036.372825283</v>
+        <v>1336036.372825284</v>
       </c>
       <c r="K2" t="n">
         <v>1336036.372825283</v>
       </c>
       <c r="L2" t="n">
-        <v>1471232.523514663</v>
+        <v>1471232.523514664</v>
       </c>
       <c r="M2" t="n">
         <v>1471232.523514664</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>614247.5715792079</v>
+        <v>619095.9472656923</v>
       </c>
       <c r="C4" t="n">
-        <v>612495.6628399484</v>
+        <v>617344.0385264327</v>
       </c>
       <c r="D4" t="n">
-        <v>610741.3775271378</v>
+        <v>615589.7532136219</v>
       </c>
       <c r="E4" t="n">
-        <v>532123.6038252711</v>
+        <v>536922.2846154375</v>
       </c>
       <c r="F4" t="n">
-        <v>556398.2196192667</v>
+        <v>561196.9004094332</v>
       </c>
       <c r="G4" t="n">
-        <v>581187.6277435899</v>
+        <v>585986.3085337563</v>
       </c>
       <c r="H4" t="n">
-        <v>579514.6928034927</v>
+        <v>584313.3735936615</v>
       </c>
       <c r="I4" t="n">
-        <v>577839.4224190661</v>
+        <v>582638.1032092324</v>
       </c>
       <c r="J4" t="n">
-        <v>520323.0592843113</v>
+        <v>524998.4738086243</v>
       </c>
       <c r="K4" t="n">
-        <v>518858.3176303694</v>
+        <v>523533.7321546826</v>
       </c>
       <c r="L4" t="n">
-        <v>581043.8351797319</v>
+        <v>585765.7481143259</v>
       </c>
       <c r="M4" t="n">
-        <v>579313.7164781798</v>
+        <v>584035.6294127734</v>
       </c>
       <c r="N4" t="n">
-        <v>577581.1101536278</v>
+        <v>582303.0230882212</v>
       </c>
       <c r="O4" t="n">
-        <v>494869.5309141541</v>
+        <v>499544.9454384672</v>
       </c>
       <c r="P4" t="n">
-        <v>454063.7935190182</v>
+        <v>458739.2080433314</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>526516.8265777044</v>
+        <v>521668.4508912203</v>
       </c>
       <c r="C6" t="n">
-        <v>814796.7353169641</v>
+        <v>809948.3596304802</v>
       </c>
       <c r="D6" t="n">
-        <v>816551.0206297738</v>
+        <v>811702.6449432902</v>
       </c>
       <c r="E6" t="n">
-        <v>570704.498656012</v>
+        <v>565905.8178658456</v>
       </c>
       <c r="F6" t="n">
-        <v>758549.6810811338</v>
+        <v>753751.0002909668</v>
       </c>
       <c r="G6" t="n">
-        <v>786453.1123525802</v>
+        <v>781654.4315624143</v>
       </c>
       <c r="H6" t="n">
-        <v>810526.0472926775</v>
+        <v>805727.366502514</v>
       </c>
       <c r="I6" t="n">
-        <v>812201.3176771043</v>
+        <v>807402.6368869381</v>
       </c>
       <c r="J6" t="n">
-        <v>340903.3885409721</v>
+        <v>336227.9740166593</v>
       </c>
       <c r="K6" t="n">
-        <v>730464.1301949134</v>
+        <v>725788.7156706008</v>
       </c>
       <c r="L6" t="n">
-        <v>743526.2093349309</v>
+        <v>738804.2964003379</v>
       </c>
       <c r="M6" t="n">
-        <v>820456.3280364843</v>
+        <v>815734.4151018907</v>
       </c>
       <c r="N6" t="n">
-        <v>822188.9343610357</v>
+        <v>817467.0214264428</v>
       </c>
       <c r="O6" t="n">
-        <v>661984.2804791307</v>
+        <v>657308.8659548179</v>
       </c>
       <c r="P6" t="n">
-        <v>692190.594810519</v>
+        <v>687515.1802862054</v>
       </c>
     </row>
   </sheetData>
@@ -26990,7 +26990,7 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -27005,7 +27005,7 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27433,7 +27433,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>307.3903671255647</v>
+        <v>400</v>
       </c>
       <c r="C2" t="n">
         <v>400</v>
@@ -27484,10 +27484,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>400</v>
+        <v>307.3903671255649</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27502,7 +27502,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27527,7 +27527,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>41.0931765820842</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>25.64973322841081</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
@@ -27606,19 +27606,19 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>355.4483345055833</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,16 +27642,16 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
         <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9583912744579</v>
+        <v>283.0589857278734</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
@@ -27660,7 +27660,7 @@
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27724,22 +27724,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
       </c>
       <c r="V5" t="n">
-        <v>307.3903671255647</v>
+        <v>400</v>
       </c>
       <c r="W5" t="n">
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>400</v>
+        <v>307.3903671255648</v>
       </c>
     </row>
     <row r="6">
@@ -27752,7 +27752,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -27794,16 +27794,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>76.45355315257606</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>342.2743756165773</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27812,10 +27812,10 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,16 +27828,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>399.4459404693707</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
@@ -27882,7 +27882,7 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>280.5595830478117</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
         <v>150.9583912744579</v>
@@ -27891,7 +27891,7 @@
         <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>306.4306086145857</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27964,10 +27964,10 @@
         <v>400</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V8" t="n">
-        <v>400</v>
+        <v>56.51176829727035</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
@@ -27998,7 +27998,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>281.9106179544541</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>115.3536407070569</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28074,7 +28074,7 @@
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
@@ -28086,13 +28086,13 @@
         <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
+        <v>176.6334556201183</v>
+      </c>
+      <c r="J10" t="n">
         <v>400</v>
       </c>
-      <c r="J10" t="n">
-        <v>35.26894883590776</v>
-      </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28119,10 +28119,10 @@
         <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>223.5311105473465</v>
       </c>
       <c r="U10" t="n">
-        <v>353.3910184833001</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28131,10 +28131,10 @@
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28244,7 +28244,7 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J12" t="n">
         <v>225</v>
@@ -28253,13 +28253,13 @@
         <v>225</v>
       </c>
       <c r="L12" t="n">
-        <v>71.03760616835928</v>
+        <v>225</v>
       </c>
       <c r="M12" t="n">
         <v>225</v>
       </c>
       <c r="N12" t="n">
-        <v>225</v>
+        <v>26.99048536749049</v>
       </c>
       <c r="O12" t="n">
         <v>225</v>
@@ -28268,7 +28268,7 @@
         <v>225</v>
       </c>
       <c r="Q12" t="n">
-        <v>173.0792650904796</v>
+        <v>225</v>
       </c>
       <c r="R12" t="n">
         <v>225</v>
@@ -28481,16 +28481,16 @@
         <v>251</v>
       </c>
       <c r="I15" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J15" t="n">
         <v>251</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>251</v>
+        <v>26.99264054024945</v>
       </c>
       <c r="M15" t="n">
         <v>251</v>
@@ -28499,13 +28499,13 @@
         <v>251</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="P15" t="n">
-        <v>166.1982915220772</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>251</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>251</v>
@@ -28721,28 +28721,28 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>44.46493928527497</v>
       </c>
       <c r="O18" t="n">
-        <v>217.5442043757547</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988283496</v>
       </c>
       <c r="S20" t="n">
         <v>279</v>
@@ -28958,28 +28958,28 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
-        <v>217.5442043757546</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>279</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>279</v>
+        <v>217.5442043757548</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29192,28 +29192,28 @@
         <v>279</v>
       </c>
       <c r="I24" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>44.46493928527497</v>
+      </c>
+      <c r="O24" t="n">
         <v>279</v>
       </c>
-      <c r="J24" t="n">
+      <c r="P24" t="n">
         <v>279</v>
-      </c>
-      <c r="K24" t="n">
-        <v>261.5913251766236</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>173.0792650904796</v>
@@ -29432,7 +29432,7 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
-        <v>78.91122027701098</v>
+        <v>225</v>
       </c>
       <c r="K27" t="n">
         <v>225</v>
@@ -29441,7 +29441,7 @@
         <v>225</v>
       </c>
       <c r="M27" t="n">
-        <v>225</v>
+        <v>26.99048536749062</v>
       </c>
       <c r="N27" t="n">
         <v>225</v>
@@ -29453,7 +29453,7 @@
         <v>225</v>
       </c>
       <c r="Q27" t="n">
-        <v>173.0792650904796</v>
+        <v>225</v>
       </c>
       <c r="R27" t="n">
         <v>225</v>
@@ -29824,7 +29824,7 @@
         <v>291</v>
       </c>
       <c r="I32" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S32" t="n">
         <v>291</v>
@@ -29903,19 +29903,19 @@
         <v>291</v>
       </c>
       <c r="I33" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>127.8102101760009</v>
+      </c>
+      <c r="M33" t="n">
         <v>291</v>
-      </c>
-      <c r="J33" t="n">
-        <v>291</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>53.93659606734946</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -29973,7 +29973,7 @@
         <v>291</v>
       </c>
       <c r="F34" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
       <c r="G34" t="n">
         <v>291</v>
@@ -30140,10 +30140,10 @@
         <v>291</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>291</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -30158,13 +30158,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>127.8102101760008</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>173.0792650904796</v>
+        <v>227.0158611578291</v>
       </c>
       <c r="R36" t="n">
         <v>291</v>
@@ -30280,7 +30280,7 @@
         <v>291</v>
       </c>
       <c r="C38" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="D38" t="n">
         <v>291</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S38" t="n">
         <v>291</v>
@@ -30377,19 +30377,19 @@
         <v>291</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>291</v>
       </c>
       <c r="J39" t="n">
+        <v>53.93659606734933</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>291</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>127.8102101760011</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -30632,13 +30632,13 @@
         <v>213</v>
       </c>
       <c r="O42" t="n">
-        <v>9.611785124016606</v>
+        <v>213</v>
       </c>
       <c r="P42" t="n">
-        <v>213</v>
+        <v>49.53252003353703</v>
       </c>
       <c r="Q42" t="n">
-        <v>213</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
         <v>213</v>
@@ -30854,7 +30854,7 @@
         <v>187</v>
       </c>
       <c r="J45" t="n">
-        <v>166.9136026975345</v>
+        <v>187</v>
       </c>
       <c r="K45" t="n">
         <v>187</v>
@@ -30872,7 +30872,7 @@
         <v>187</v>
       </c>
       <c r="P45" t="n">
-        <v>187</v>
+        <v>161.0457473881675</v>
       </c>
       <c r="Q45" t="n">
         <v>187</v>
@@ -30930,7 +30930,7 @@
         <v>187</v>
       </c>
       <c r="I46" t="n">
-        <v>176.6334556201183</v>
+        <v>187</v>
       </c>
       <c r="J46" t="n">
         <v>187</v>
@@ -34746,10 +34746,10 @@
         <v>814</v>
       </c>
       <c r="K2" t="n">
+        <v>814</v>
+      </c>
+      <c r="L2" t="n">
         <v>814.0000000000001</v>
-      </c>
-      <c r="L2" t="n">
-        <v>814</v>
       </c>
       <c r="M2" t="n">
         <v>814</v>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
@@ -34892,19 +34892,19 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>110.4044616640532</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,16 +34928,16 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>132.1005944534155</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
@@ -34946,7 +34946,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -35114,16 +35114,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>118.4650356324142</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
@@ -35168,7 +35168,7 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>70.535016541554</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -35177,7 +35177,7 @@
         <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35220,7 +35220,7 @@
         <v>814</v>
       </c>
       <c r="K8" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -35229,7 +35229,7 @@
         <v>814</v>
       </c>
       <c r="N8" t="n">
-        <v>814</v>
+        <v>814.0000000000045</v>
       </c>
       <c r="O8" t="n">
         <v>814</v>
@@ -35360,7 +35360,7 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
@@ -35372,13 +35372,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35405,10 +35405,10 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>13.50654404108874</v>
       </c>
       <c r="U10" t="n">
-        <v>202.4326272088421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -35417,10 +35417,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,13 +35454,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>459.6877287841431</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
-        <v>814</v>
+        <v>532.5214919778891</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35472,10 +35472,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,7 +35530,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>350.2086062376757</v>
@@ -35539,13 +35539,13 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>345.1289815170463</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
         <v>311.9500421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>359.6265501086548</v>
+        <v>161.6170354761453</v>
       </c>
       <c r="O12" t="n">
         <v>466.4570219027464</v>
@@ -35554,7 +35554,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>51.92073490952041</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
+        <v>814.0000000000001</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>814</v>
       </c>
-      <c r="M14" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N14" t="n">
-        <v>619.4144644189528</v>
-      </c>
-      <c r="O14" t="n">
-        <v>161.5508809199775</v>
-      </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>435.2066046459232</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,16 +35767,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>33.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>125.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K15" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>525.0913753486871</v>
+        <v>301.0840158889364</v>
       </c>
       <c r="M15" t="n">
         <v>337.9500421645043</v>
@@ -35785,13 +35785,13 @@
         <v>385.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>241.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>279.8642960367304</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>77.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35934,22 +35934,22 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L17" t="n">
-        <v>161.5508809199773</v>
+        <v>39.94487430485674</v>
       </c>
       <c r="M17" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>814</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36007,28 +36007,28 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>125.2086062376757</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>365.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
-        <v>134.6265501086548</v>
+        <v>179.0914893939298</v>
       </c>
       <c r="O18" t="n">
-        <v>459.0012262785011</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P18" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36168,28 +36168,28 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>636.0728042610074</v>
       </c>
       <c r="L20" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P20" t="n">
-        <v>113.7832223189554</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>5.512089101654111e-11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36244,13 +36244,13 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>342.7528106134303</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L21" t="n">
-        <v>553.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
         <v>86.95004216450428</v>
@@ -36259,13 +36259,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P21" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>105.9207349095204</v>
+        <v>44.46493928527515</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36408,13 +36408,13 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>337.9359563968417</v>
+        <v>39.94487430485688</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -36478,13 +36478,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>61.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>452.6951798174148</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
         <v>274.091375348687</v>
@@ -36493,13 +36493,13 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>134.6265501086548</v>
+        <v>179.0914893939298</v>
       </c>
       <c r="O24" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -36642,13 +36642,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>314.0531751575542</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>516.0089179080152</v>
+        <v>57.06209306554275</v>
       </c>
       <c r="N26" t="n">
         <v>619.4144644189528</v>
@@ -36657,7 +36657,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>773.0000000000266</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36718,7 +36718,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>204.1198265146867</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K27" t="n">
         <v>416.1038546407913</v>
@@ -36727,7 +36727,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
-        <v>311.9500421645043</v>
+        <v>113.9405275319949</v>
       </c>
       <c r="N27" t="n">
         <v>359.6265501086548</v>
@@ -36739,7 +36739,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>51.92073490952041</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36876,10 +36876,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>314.0531751575203</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -36891,13 +36891,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>773.0000000000339</v>
       </c>
       <c r="P29" t="n">
         <v>773.0000000000339</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>379.3442944406408</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37116,7 +37116,7 @@
         <v>773.0000000000412</v>
       </c>
       <c r="K32" t="n">
-        <v>773</v>
+        <v>727.1079320762516</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
@@ -37125,7 +37125,7 @@
         <v>773.0000000000412</v>
       </c>
       <c r="N32" t="n">
-        <v>727.1079320760797</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="O32" t="n">
         <v>773.0000000000412</v>
@@ -37189,19 +37189,19 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>73.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>416.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K33" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>274.091375348687</v>
+        <v>401.9015855246878</v>
       </c>
       <c r="M33" t="n">
-        <v>140.8866382318537</v>
+        <v>377.9500421645043</v>
       </c>
       <c r="N33" t="n">
         <v>134.6265501086548</v>
@@ -37259,7 +37259,7 @@
         <v>10.01909516304346</v>
       </c>
       <c r="F34" t="n">
-        <v>16.61714403225807</v>
+        <v>16.61714403228201</v>
       </c>
       <c r="G34" t="n">
         <v>45.95612715846997</v>
@@ -37353,10 +37353,10 @@
         <v>773.0000000000484</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320761796</v>
+        <v>727.1079320762628</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>773.0000000000001</v>
       </c>
       <c r="M35" t="n">
         <v>773.0000000000484</v>
@@ -37426,10 +37426,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>73.87361410865147</v>
       </c>
       <c r="J36" t="n">
-        <v>125.2086062376757</v>
+        <v>416.2086062376757</v>
       </c>
       <c r="K36" t="n">
         <v>191.1038546407913</v>
@@ -37444,13 +37444,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O36" t="n">
-        <v>369.2672320787472</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>404.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>53.93659606734953</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37590,10 +37590,10 @@
         <v>773.0000000000557</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320763394</v>
+        <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>727.1079320762449</v>
       </c>
       <c r="M38" t="n">
         <v>773.0000000000557</v>
@@ -37663,19 +37663,19 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>73.87361410865147</v>
       </c>
       <c r="J39" t="n">
-        <v>416.2086062376757</v>
+        <v>179.145202305025</v>
       </c>
       <c r="K39" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L39" t="n">
-        <v>401.9015855246881</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M39" t="n">
-        <v>86.95004216450428</v>
+        <v>377.9500421645043</v>
       </c>
       <c r="N39" t="n">
         <v>134.6265501086548</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>379.3442944406461</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>772.9999999999999</v>
+        <v>773</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>354.8631703024262</v>
+        <v>773.000000000063</v>
       </c>
       <c r="P41" t="n">
-        <v>773.000000000063</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37918,13 +37918,13 @@
         <v>347.6265501086548</v>
       </c>
       <c r="O42" t="n">
-        <v>251.068807026763</v>
+        <v>454.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>326.6660045146532</v>
+        <v>163.1985245481902</v>
       </c>
       <c r="Q42" t="n">
-        <v>39.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -38067,7 +38067,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>772.9999999999999</v>
+        <v>765.4397879755212</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38082,7 +38082,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>435.4691769176098</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>292.1222089352103</v>
+        <v>312.2086062376757</v>
       </c>
       <c r="K45" t="n">
         <v>378.1038546407913</v>
@@ -38158,7 +38158,7 @@
         <v>428.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>300.6660045146532</v>
+        <v>274.7117519028208</v>
       </c>
       <c r="Q45" t="n">
         <v>13.92073490952041</v>
@@ -38216,7 +38216,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>10.36654437988173</v>
       </c>
       <c r="J46" t="n">
         <v>151.7310511640922</v>
